--- a/artfynd/A 68085-2019 artfynd.xlsx
+++ b/artfynd/A 68085-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 68085-2019 artfynd.xlsx
+++ b/artfynd/A 68085-2019 artfynd.xlsx
@@ -3604,7 +3604,7 @@
         <v>117317304</v>
       </c>
       <c r="B28" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>117317348</v>
       </c>
       <c r="B29" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
